--- a/reference/worldgen-compare.xlsx
+++ b/reference/worldgen-compare.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Skylar\Documents\01_Personal_Docs\Git\VS-HaveYourBerriesAndEatThemToo\reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6361117E-F73D-443E-8396-0E33BDF8B728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5720F76D-4855-4944-8A21-C24581D9B10D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58215" yWindow="6870" windowWidth="29475" windowHeight="14115" xr2:uid="{FA07493C-3708-4AAD-88CF-9913F3C8CD29}"/>
+    <workbookView xWindow="55185" yWindow="5850" windowWidth="29475" windowHeight="14115" xr2:uid="{FA07493C-3708-4AAD-88CF-9913F3C8CD29}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="44">
   <si>
     <t>Wildcraft</t>
   </si>
@@ -116,9 +116,6 @@
     <t>cloudberry</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>Offset X/Y: 0 avg, 15 var.</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
   </si>
   <si>
     <t>Use values, use vanilla placement</t>
-  </si>
-  <si>
-    <t>Found Naturally</t>
   </si>
   <si>
     <t>Use values, remove placement</t>
@@ -668,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -676,7 +670,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -688,12 +682,198 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -712,219 +892,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="0"/>
@@ -940,17 +918,6 @@
       <fill>
         <patternFill>
           <bgColor theme="6" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1321,159 +1288,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65"/>
-      <c r="B1" s="9" t="s">
+      <c r="A1" s="77"/>
+      <c r="B1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="12" t="s">
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="14"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+      <c r="P1" s="75"/>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="75"/>
+      <c r="S1" s="75"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="75"/>
+      <c r="V1" s="76"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66"/>
-      <c r="B2" s="46" t="s">
+      <c r="A2" s="78"/>
+      <c r="B2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="E2" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="46" t="s">
+      <c r="L2" s="70"/>
+      <c r="M2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="48" t="s">
+      <c r="O2" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="49" t="s">
+      <c r="P2" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="50" t="s">
+      <c r="Q2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="51" t="s">
+      <c r="R2" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="52" t="s">
+      <c r="S2" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="53" t="s">
+      <c r="T2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="U2" s="54" t="s">
+      <c r="U2" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="V2" s="46" t="s">
         <v>28</v>
-      </c>
-      <c r="V2" s="55" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="8">
         <v>-2</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="10">
         <v>-5</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="12">
         <v>0</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="14">
         <v>-10</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="16">
         <v>-10</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="16">
         <v>6</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="18">
         <v>12</v>
       </c>
       <c r="I3" s="3">
         <v>-14</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="20">
         <v>10</v>
       </c>
       <c r="K3" s="2">
         <v>-4</v>
       </c>
-      <c r="L3" s="57" t="s">
+      <c r="L3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="56">
+      <c r="M3" s="47">
         <v>-2</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="27">
         <v>-3</v>
       </c>
-      <c r="O3" s="32">
+      <c r="O3" s="25">
         <v>0</v>
       </c>
-      <c r="P3" s="35">
+      <c r="P3" s="28">
         <v>-2</v>
       </c>
-      <c r="Q3" s="36">
+      <c r="Q3" s="29">
         <v>-2</v>
       </c>
-      <c r="R3" s="36">
+      <c r="R3" s="29">
         <v>-2</v>
       </c>
-      <c r="S3" s="37">
+      <c r="S3" s="30">
         <v>10</v>
       </c>
-      <c r="T3" s="38">
+      <c r="T3" s="31">
         <v>-20</v>
       </c>
-      <c r="U3" s="27">
+      <c r="U3" s="20">
         <v>-2</v>
       </c>
       <c r="V3" s="2">
@@ -1481,67 +1448,67 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
-        <v>18</v>
-      </c>
-      <c r="C4" s="17">
+      <c r="B4" s="8">
+        <v>18</v>
+      </c>
+      <c r="C4" s="10">
         <v>16</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="12">
         <v>20</v>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="14">
         <v>10</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="16">
         <v>12</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="16">
         <v>24</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="18">
         <v>18</v>
       </c>
       <c r="I4" s="3">
         <v>8</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="21">
         <v>18</v>
       </c>
       <c r="K4" s="2">
         <v>18</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="8">
         <v>23</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="10">
         <v>22</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="12">
         <v>24</v>
       </c>
-      <c r="P4" s="21">
-        <v>18</v>
-      </c>
-      <c r="Q4" s="23">
-        <v>18</v>
-      </c>
-      <c r="R4" s="23">
-        <v>18</v>
-      </c>
-      <c r="S4" s="25">
+      <c r="P4" s="14">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>18</v>
+      </c>
+      <c r="R4" s="16">
+        <v>18</v>
+      </c>
+      <c r="S4" s="18">
         <v>22</v>
       </c>
-      <c r="T4" s="39">
+      <c r="T4" s="32">
         <v>-3</v>
       </c>
-      <c r="U4" s="28">
+      <c r="U4" s="21">
         <v>23</v>
       </c>
       <c r="V4" s="2">
@@ -1549,67 +1516,67 @@
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="8">
         <v>0.5</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="10">
         <v>0.5</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="12">
         <v>0.5</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="14">
         <v>0.6</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="16">
         <v>0.6</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="16">
         <v>0.5</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="18">
         <v>0.6</v>
       </c>
       <c r="I5" s="3">
         <v>0.5</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="21">
         <v>0.5</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="8">
         <v>0.3</v>
       </c>
-      <c r="N5" s="17">
+      <c r="N5" s="10">
         <v>0.3</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="12">
         <v>0.3</v>
       </c>
-      <c r="P5" s="21">
+      <c r="P5" s="14">
         <v>0.3</v>
       </c>
-      <c r="Q5" s="23">
+      <c r="Q5" s="16">
         <v>0.45</v>
       </c>
-      <c r="R5" s="23">
+      <c r="R5" s="16">
         <v>0.45</v>
       </c>
-      <c r="S5" s="25">
+      <c r="S5" s="18">
         <v>0.45</v>
       </c>
-      <c r="T5" s="39">
+      <c r="T5" s="32">
         <v>0.5</v>
       </c>
-      <c r="U5" s="28">
+      <c r="U5" s="21">
         <v>0.35</v>
       </c>
       <c r="V5" s="2">
@@ -1617,67 +1584,67 @@
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="12">
         <v>1</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="14">
         <v>1</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="16">
         <v>1</v>
       </c>
-      <c r="G6" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="25" t="s">
+      <c r="G6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K6" s="2">
         <v>0.8</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="8">
         <v>0.7</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="10">
         <v>0.7</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="12">
         <v>0.7</v>
       </c>
-      <c r="P6" s="21">
+      <c r="P6" s="14">
         <v>0.7</v>
       </c>
-      <c r="Q6" s="23">
+      <c r="Q6" s="16">
         <v>1</v>
       </c>
-      <c r="R6" s="23">
+      <c r="R6" s="16">
         <v>1</v>
       </c>
-      <c r="S6" s="25">
+      <c r="S6" s="18">
         <v>1</v>
       </c>
-      <c r="T6" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="U6" s="28" t="s">
+      <c r="T6" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="U6" s="21" t="s">
         <v>18</v>
       </c>
       <c r="V6" s="2" t="s">
@@ -1685,67 +1652,67 @@
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="25" t="s">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="3">
         <v>0.6</v>
       </c>
-      <c r="J7" s="28" t="s">
+      <c r="J7" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="15">
+      <c r="L7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="8">
         <v>0.25</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="10">
         <v>0.25</v>
       </c>
-      <c r="O7" s="45">
+      <c r="O7" s="12">
         <v>0.25</v>
       </c>
-      <c r="P7" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="S7" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="T7" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="U7" s="28" t="s">
+      <c r="P7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="S7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="U7" s="21" t="s">
         <v>18</v>
       </c>
       <c r="V7" s="2">
@@ -1753,67 +1720,67 @@
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="25" t="s">
+      <c r="A8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="J8" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="M8" s="15">
+      <c r="L8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" s="8">
         <v>0.6</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="10">
         <v>0.6</v>
       </c>
-      <c r="O8" s="45">
+      <c r="O8" s="12">
         <v>0.6</v>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="14">
         <v>0.5</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="16">
         <v>1</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="16">
         <v>1</v>
       </c>
-      <c r="S8" s="25">
+      <c r="S8" s="18">
         <v>1</v>
       </c>
-      <c r="T8" s="39">
+      <c r="T8" s="32">
         <v>0.5</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="21">
         <v>0.8</v>
       </c>
       <c r="V8" s="2" t="s">
@@ -1821,67 +1788,67 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="8">
         <v>0.3</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="10">
         <v>0.4</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="12">
         <v>0.5</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="23">
+      <c r="E9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="16">
         <v>0.45</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="18">
         <v>0.4</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="21">
         <v>0.5</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="P9" s="21">
+      <c r="M9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="14">
         <v>0.5</v>
       </c>
-      <c r="Q9" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="R9" s="23">
+      <c r="Q9" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" s="16">
         <v>0.6</v>
       </c>
-      <c r="S9" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="T9" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="U9" s="28">
+      <c r="S9" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="T9" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="U9" s="21">
         <v>0.5</v>
       </c>
       <c r="V9" s="2" t="s">
@@ -1889,67 +1856,67 @@
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="14">
         <v>0.5</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="16">
         <v>0.3</v>
       </c>
-      <c r="G10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="25" t="s">
+      <c r="G10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="3">
         <v>0.6</v>
       </c>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K10" s="2">
         <v>0.5</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="8">
         <v>0.5</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="10">
         <v>0.4</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="12">
         <v>0.4</v>
       </c>
-      <c r="P10" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q10" s="23">
+      <c r="P10" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="16">
         <v>0.7</v>
       </c>
-      <c r="R10" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="S10" s="25">
+      <c r="R10" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" s="18">
         <v>0.4</v>
       </c>
-      <c r="T10" s="39">
+      <c r="T10" s="32">
         <v>0.7</v>
       </c>
-      <c r="U10" s="28" t="s">
+      <c r="U10" s="21" t="s">
         <v>18</v>
       </c>
       <c r="V10" s="2">
@@ -1957,67 +1924,67 @@
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="8">
         <v>0.62</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="10">
         <v>0.62</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="12">
         <v>0.62</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="14">
         <v>0.03</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="16">
         <v>0.16</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="16">
         <v>0.13</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="18" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="3">
         <v>0.12</v>
       </c>
-      <c r="J11" s="28" t="s">
+      <c r="J11" s="21" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="2">
         <v>0.16</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="8">
         <v>0.62</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="10">
         <v>0.62</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="12">
         <v>0.62</v>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="14">
         <v>0.85</v>
       </c>
-      <c r="Q11" s="23">
+      <c r="Q11" s="16">
         <v>0.4</v>
       </c>
-      <c r="R11" s="23">
+      <c r="R11" s="16">
         <v>0.4</v>
       </c>
-      <c r="S11" s="25">
+      <c r="S11" s="18">
         <v>0.4</v>
       </c>
-      <c r="T11" s="39">
+      <c r="T11" s="32">
         <v>0.1</v>
       </c>
-      <c r="U11" s="28">
+      <c r="U11" s="21">
         <v>0.8</v>
       </c>
       <c r="V11" s="2">
@@ -2025,67 +1992,67 @@
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="8">
         <v>0.04</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="10">
         <v>0.04</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="12">
         <v>0.02</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="14">
         <v>0.16</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="16">
         <v>0.05</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="16">
         <v>0.08</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="18">
         <v>0.03</v>
       </c>
       <c r="I12" s="3">
         <v>0.02</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="21">
         <v>0.03</v>
       </c>
       <c r="K12" s="2">
         <v>0.02</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="8">
         <v>0.12</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="10">
         <v>0.12</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="12">
         <v>0.03</v>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="14">
         <v>0.1</v>
       </c>
-      <c r="Q12" s="23">
+      <c r="Q12" s="16">
         <v>0.08</v>
       </c>
-      <c r="R12" s="23">
+      <c r="R12" s="16">
         <v>0.08</v>
       </c>
-      <c r="S12" s="25">
+      <c r="S12" s="18">
         <v>0.08</v>
       </c>
-      <c r="T12" s="39">
+      <c r="T12" s="32">
         <v>0.02</v>
       </c>
-      <c r="U12" s="28">
+      <c r="U12" s="21">
         <v>0.08</v>
       </c>
       <c r="V12" s="2">
@@ -2093,67 +2060,67 @@
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="8">
         <v>2</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="10">
         <v>2</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="12">
         <v>2</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="14">
         <v>5</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="16">
         <v>5</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="16">
         <v>7</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="18">
         <v>3</v>
       </c>
       <c r="I13" s="3">
         <v>5</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="21">
         <v>3</v>
       </c>
       <c r="K13" s="2">
         <v>2</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="8">
         <v>2</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="10">
         <v>2</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="12">
         <v>2</v>
       </c>
-      <c r="P13" s="21">
+      <c r="P13" s="14">
         <v>5</v>
       </c>
-      <c r="Q13" s="23">
+      <c r="Q13" s="16">
         <v>5</v>
       </c>
-      <c r="R13" s="23">
+      <c r="R13" s="16">
         <v>10</v>
       </c>
-      <c r="S13" s="25">
+      <c r="S13" s="18">
         <v>5</v>
       </c>
-      <c r="T13" s="39">
+      <c r="T13" s="32">
         <v>10</v>
       </c>
-      <c r="U13" s="28">
+      <c r="U13" s="21">
         <v>7</v>
       </c>
       <c r="V13" s="2">
@@ -2161,67 +2128,67 @@
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="8">
         <v>8</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="10">
         <v>8</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="12">
         <v>8</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="14">
         <v>12</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="16">
         <v>12</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="16">
         <v>15</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="18">
         <v>10</v>
       </c>
       <c r="I14" s="3">
         <v>10</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="21">
         <v>10</v>
       </c>
       <c r="K14" s="2">
         <v>5</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="8">
         <v>4</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="10">
         <v>4</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="12">
         <v>4</v>
       </c>
-      <c r="P14" s="21">
+      <c r="P14" s="14">
         <v>12</v>
       </c>
-      <c r="Q14" s="23">
+      <c r="Q14" s="16">
         <v>12</v>
       </c>
-      <c r="R14" s="23">
+      <c r="R14" s="16">
         <v>24</v>
       </c>
-      <c r="S14" s="25">
+      <c r="S14" s="18">
         <v>12</v>
       </c>
-      <c r="T14" s="39">
+      <c r="T14" s="32">
         <v>8</v>
       </c>
-      <c r="U14" s="28">
+      <c r="U14" s="21">
         <v>10</v>
       </c>
       <c r="V14" s="2">
@@ -2229,67 +2196,67 @@
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="26" t="s">
+      <c r="E15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="19" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="29" t="s">
+      <c r="J15" s="22" t="s">
         <v>12</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="N15" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O15" s="20" t="s">
+      <c r="O15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="P15" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q15" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="R15" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="S15" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="T15" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="U15" s="29" t="s">
+      <c r="P15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="R15" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="S15" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="T15" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="U15" s="22" t="s">
         <v>18</v>
       </c>
       <c r="V15" s="5" t="s">
@@ -2297,339 +2264,369 @@
       </c>
     </row>
     <row r="16" spans="1:22" ht="60" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="32" t="s">
+      <c r="F16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="P16" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" s="32" t="s">
+      <c r="Q16" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="R16" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="59" t="s">
+      <c r="S16" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="N16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="O16" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="P16" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q16" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="R16" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="S16" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="T16" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="U16" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="V16" s="70" t="s">
+      <c r="T16" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="U16" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="V16" s="55" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="42" t="s">
+      <c r="B17" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="42" t="s">
+      <c r="G17" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="61" t="s">
+      <c r="H17" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="52" t="s">
         <v>18</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="M17" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="O17" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="P17" s="42" t="s">
+      <c r="M17" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="P17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="R17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="Q17" s="42" t="s">
+      <c r="S17" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="T17" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="R17" s="42" t="s">
+      <c r="U17" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="S17" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="U17" s="42" t="s">
+      <c r="V17" s="56" t="s">
         <v>38</v>
-      </c>
-      <c r="V17" s="71" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="72" t="s">
+      <c r="C18" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="M18" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="N18" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="72" t="s">
+      <c r="O18" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="72" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="72" t="s">
-        <v>45</v>
-      </c>
-      <c r="L18" s="69" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" s="75" t="s">
-        <v>42</v>
-      </c>
-      <c r="N18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="O18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="P18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="R18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="S18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="T18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="U18" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="V18" s="76" t="s">
-        <v>42</v>
+      <c r="P18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="R18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="S18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="T18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="U18" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="V18" s="62" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="63"/>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
-      <c r="J19" s="73"/>
-      <c r="K19" s="73"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="77"/>
-      <c r="N19" s="73"/>
-      <c r="O19" s="73"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="73"/>
-      <c r="S19" s="73"/>
-      <c r="T19" s="73"/>
-      <c r="U19" s="73"/>
-      <c r="V19" s="78"/>
+      <c r="A19" s="69"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="63"/>
     </row>
     <row r="20" spans="1:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="64"/>
-      <c r="B20" s="74"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="64"/>
-      <c r="M20" s="79"/>
-      <c r="N20" s="74"/>
-      <c r="O20" s="74"/>
-      <c r="P20" s="74"/>
-      <c r="Q20" s="74"/>
-      <c r="R20" s="74"/>
-      <c r="S20" s="74"/>
-      <c r="T20" s="74"/>
-      <c r="U20" s="74"/>
-      <c r="V20" s="80"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="70"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
+      <c r="V20" s="64"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="72" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="D21" s="68" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="68"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="68"/>
+      <c r="A21" s="59"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="57"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="57"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="57"/>
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+      <c r="T21" s="57"/>
+      <c r="U21" s="57"/>
+      <c r="V21" s="57"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="81"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
+      <c r="A22" s="60"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="58"/>
+      <c r="T22" s="58"/>
+      <c r="U22" s="58"/>
+      <c r="V22" s="58"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="81"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
+      <c r="A23" s="60"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="58"/>
+      <c r="U23" s="58"/>
+      <c r="V23" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="M1:V1"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="F18:F20"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="M18:M20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="O18:O20"/>
+    <mergeCell ref="P18:P20"/>
+    <mergeCell ref="G18:G20"/>
+    <mergeCell ref="H18:H20"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="K18:K20"/>
+    <mergeCell ref="L18:L20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="L21:L23"/>
+    <mergeCell ref="S18:S20"/>
+    <mergeCell ref="T18:T20"/>
+    <mergeCell ref="U18:U20"/>
+    <mergeCell ref="V18:V20"/>
+    <mergeCell ref="Q18:Q20"/>
+    <mergeCell ref="R18:R20"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J21:J23"/>
+    <mergeCell ref="K21:K23"/>
     <mergeCell ref="S21:S23"/>
     <mergeCell ref="T21:T23"/>
     <mergeCell ref="U21:U23"/>
@@ -2640,56 +2637,15 @@
     <mergeCell ref="P21:P23"/>
     <mergeCell ref="Q21:Q23"/>
     <mergeCell ref="R21:R23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="J21:J23"/>
-    <mergeCell ref="K21:K23"/>
-    <mergeCell ref="L21:L23"/>
-    <mergeCell ref="S18:S20"/>
-    <mergeCell ref="T18:T20"/>
-    <mergeCell ref="U18:U20"/>
-    <mergeCell ref="V18:V20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E23"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="M18:M20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="O18:O20"/>
-    <mergeCell ref="P18:P20"/>
-    <mergeCell ref="Q18:Q20"/>
-    <mergeCell ref="R18:R20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="H18:H20"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="J18:J20"/>
-    <mergeCell ref="K18:K20"/>
-    <mergeCell ref="L18:L20"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="L1:L2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="F18:F20"/>
   </mergeCells>
   <conditionalFormatting sqref="B16:V16">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH("X",B16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="N/A">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:V17">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="N/A">
       <formula>NOT(ISERROR(SEARCH("N/A",B16)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:V17">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",B17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
